--- a/data/input.template.xlsx
+++ b/data/input.template.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:X4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +462,81 @@
           <t>概念</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>近20日涨幅</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>近5日涨幅</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>主营业务</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>近1季度营收</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>近1季度净利润</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>近1季度净利润增速</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>近2季度营收</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>近2季度净利润</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>近2季度净利润增速</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>近3季度营收</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>近3季度净利润</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>近3季度净利润增速</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>近4季度营收</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>近4季度净利润</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>近4季度净利润增速</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -509,6 +584,81 @@
           <t>人工智能;金融科技</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>软件服务</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>10亿</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1.0亿</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>9亿</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0.9亿</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>8亿</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>0.8亿</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>7亿</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.7亿</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -556,6 +706,81 @@
           <t>地产</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>房地产开发</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>20亿</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1.5亿</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>-5%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>19亿</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1.4亿</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>-8%</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>18亿</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>1.3亿</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>-10%</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>17亿</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>1.2亿</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>-12%</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -601,6 +826,81 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>金融</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>100亿</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>20亿</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>96亿</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>19亿</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>92亿</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>18亿</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>88亿</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>17亿</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>5%</t>
         </is>
       </c>
     </row>
